--- a/data/Faym Status Test Orders-results.xlsx
+++ b/data/Faym Status Test Orders-results.xlsx
@@ -609,7 +609,7 @@
       </c>
       <c r="O2" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P2" s="19" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="O3" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P3" s="19" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="O4" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P4" s="19" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="O5" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P5" s="19" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="O6" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P6" s="19" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="O7" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P7" s="19" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="O8" s="18" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P8" s="19" t="inlineStr">
@@ -28097,12 +28097,12 @@
       </c>
       <c r="O2" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P2" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-07 (24 day(s) ago; delivered 2026-06-27 + 10 day window).</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-07 (25 day(s) ago; delivered 2026-06-27 + 10 day window).</t>
         </is>
       </c>
       <c r="Q2" s="21" t="n">
@@ -28180,12 +28180,12 @@
       </c>
       <c r="O3" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P3" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-04 (27 day(s) ago; delivered 2026-06-27 + 7 day window).</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-04 (28 day(s) ago; delivered 2026-06-27 + 7 day window).</t>
         </is>
       </c>
       <c r="Q3" s="21" t="n">
@@ -28263,12 +28263,12 @@
       </c>
       <c r="O4" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P4" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-07 (24 day(s) ago; delivered 2026-06-27 + 10 day window).</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-07 (25 day(s) ago; delivered 2026-06-27 + 10 day window).</t>
         </is>
       </c>
       <c r="Q4" s="21" t="n">
@@ -28346,12 +28346,12 @@
       </c>
       <c r="O5" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P5" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-12 (19 day(s) ago; delivered 2026-07-02 + 10 day window).</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-12 (20 day(s) ago; delivered 2026-07-02 + 10 day window).</t>
         </is>
       </c>
       <c r="Q5" s="21" t="n">
@@ -28429,12 +28429,12 @@
       </c>
       <c r="O6" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P6" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-16 (15 day(s) ago; delivered 2026-07-06 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '5-6 July'; the platform's own eligibility check is authoritative.</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-16 (16 day(s) ago; delivered 2026-07-06 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '5-6 July'; the platform's own eligibility check is authoritative.</t>
         </is>
       </c>
       <c r="Q6" s="21" t="n">
@@ -28512,7 +28512,7 @@
       </c>
       <c r="O7" s="23" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P7" s="24" t="inlineStr">
@@ -28595,12 +28595,12 @@
       </c>
       <c r="O8" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P8" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-16 (15 day(s) ago; delivered 2026-07-06 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '5-6 July'; the platform's own eligibility check is authoritative.</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-16 (16 day(s) ago; delivered 2026-07-06 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '5-6 July'; the platform's own eligibility check is authoritative.</t>
         </is>
       </c>
       <c r="Q8" s="21" t="n">
@@ -28678,12 +28678,12 @@
       </c>
       <c r="O9" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P9" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-16 (15 day(s) ago; delivered 2026-07-06 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '5-6 July'; the platform's own eligibility check is authoritative.</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-16 (16 day(s) ago; delivered 2026-07-06 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '5-6 July'; the platform's own eligibility check is authoritative.</t>
         </is>
       </c>
       <c r="Q9" s="21" t="n">
@@ -28761,12 +28761,12 @@
       </c>
       <c r="O10" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P10" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-16 (15 day(s) ago; delivered 2026-07-06 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '5-6 July'; the platform's own eligibility check is authoritative.</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-16 (16 day(s) ago; delivered 2026-07-06 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '5-6 July'; the platform's own eligibility check is authoritative.</t>
         </is>
       </c>
       <c r="Q10" s="21" t="n">
@@ -28844,12 +28844,12 @@
       </c>
       <c r="O11" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P11" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-17 (14 day(s) ago; delivered 2026-07-07 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '6-7 July'; the platform's own eligibility check is authoritative.</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-17 (15 day(s) ago; delivered 2026-07-07 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '6-7 July'; the platform's own eligibility check is authoritative.</t>
         </is>
       </c>
       <c r="Q11" s="21" t="n">
@@ -28927,12 +28927,12 @@
       </c>
       <c r="O12" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P12" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-17 (14 day(s) ago; delivered 2026-07-07 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '6-7 July'; the platform's own eligibility check is authoritative.</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-17 (15 day(s) ago; delivered 2026-07-07 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '6-7 July'; the platform's own eligibility check is authoritative.</t>
         </is>
       </c>
       <c r="Q12" s="21" t="n">
@@ -29010,12 +29010,12 @@
       </c>
       <c r="O13" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P13" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-19 (12 day(s) ago; delivered 2026-07-09 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '8-9 July'; the platform's own eligibility check is authoritative.</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-19 (13 day(s) ago; delivered 2026-07-09 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '8-9 July'; the platform's own eligibility check is authoritative.</t>
         </is>
       </c>
       <c r="Q13" s="21" t="n">
@@ -29093,12 +29093,12 @@
       </c>
       <c r="O14" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P14" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-19 (12 day(s) ago; delivered 2026-07-09 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '8-9 July'; the platform's own eligibility check is authoritative.</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-19 (13 day(s) ago; delivered 2026-07-09 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '8-9 July'; the platform's own eligibility check is authoritative.</t>
         </is>
       </c>
       <c r="Q14" s="21" t="n">
@@ -29176,12 +29176,12 @@
       </c>
       <c r="O15" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P15" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-19 (12 day(s) ago; delivered 2026-07-09 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '8-9 July'; the platform's own eligibility check is authoritative.</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-19 (13 day(s) ago; delivered 2026-07-09 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '8-9 July'; the platform's own eligibility check is authoritative.</t>
         </is>
       </c>
       <c r="Q15" s="21" t="n">
@@ -29259,7 +29259,7 @@
       </c>
       <c r="O16" s="23" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P16" s="24" t="inlineStr">
@@ -29342,12 +29342,12 @@
       </c>
       <c r="O17" s="21" t="inlineStr">
         <is>
-          <t>2026-07-31T02:18:13</t>
+          <t>2026-08-01T21:43:11</t>
         </is>
       </c>
       <c r="P17" s="22" t="inlineStr">
         <is>
-          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-19 (12 day(s) ago; delivered 2026-07-09 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '8-9 July'; the platform's own eligibility check is authoritative.</t>
+          <t>[DRY RUN - no return submitted] Skipped: Window closed on 2026-07-19 (13 day(s) ago; delivered 2026-07-09 + 10 day window). Delivery date was approximated from a date range. | Delivery date approximated from '8-9 July'; the platform's own eligibility check is authoritative.</t>
         </is>
       </c>
       <c r="Q17" s="21" t="n">
